--- a/data/payment-06-2026.xlsx
+++ b/data/payment-06-2026.xlsx
@@ -203,7 +203,7 @@
     <col min="1" max="1" width="35.1" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="31.05" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="16.200000000000003" customWidth="1"/>
     <col min="5" max="5" width="41.85" customWidth="1"/>
     <col min="6" max="6" width="41.85" customWidth="1"/>
     <col min="7" max="7" width="12.15" customWidth="1"/>
@@ -437,19 +437,19 @@
         </is>
       </c>
       <c r="D5" s="63">
-        <v>21091</v>
+        <v>27760</v>
       </c>
       <c r="E5" s="65">
         <v>0</v>
       </c>
       <c r="F5" s="63">
-        <v>21091</v>
+        <v>27760</v>
       </c>
       <c r="G5" s="65">
         <v>0</v>
       </c>
       <c r="H5" s="66">
-        <v>21091.00</v>
+        <v>27760.00</v>
       </c>
       <c r="I5" s="65">
         <v>0</v>
@@ -467,7 +467,7 @@
         <v>0.00</v>
       </c>
       <c r="N5" s="63">
-        <v>21091</v>
+        <v>27760</v>
       </c>
       <c r="O5" s="65">
         <v>0</v>
@@ -493,19 +493,19 @@
         </is>
       </c>
       <c r="D6" s="63">
-        <v>152553</v>
+        <v>173329</v>
       </c>
       <c r="E6" s="66">
-        <v>438.50</v>
+        <v>452.90</v>
       </c>
       <c r="F6" s="64">
-        <v>152114.50</v>
+        <v>172876.10</v>
       </c>
       <c r="G6" s="65">
         <v>0</v>
       </c>
       <c r="H6" s="66">
-        <v>152114.50</v>
+        <v>172876.10</v>
       </c>
       <c r="I6" s="65">
         <v>0</v>
@@ -520,10 +520,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="66">
-        <v>-1.50</v>
+        <v>-1.10</v>
       </c>
       <c r="N6" s="63">
-        <v>152113</v>
+        <v>172875</v>
       </c>
       <c r="O6" s="65">
         <v>0</v>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="D7" s="63">
-        <v>73463</v>
-      </c>
-      <c r="E7" s="66">
-        <v>78.80</v>
-      </c>
-      <c r="F7" s="64">
-        <v>73384.20</v>
+        <v>91530</v>
+      </c>
+      <c r="E7" s="65">
+        <v>115</v>
+      </c>
+      <c r="F7" s="63">
+        <v>91415</v>
       </c>
       <c r="G7" s="65">
         <v>0</v>
       </c>
       <c r="H7" s="66">
-        <v>73384.20</v>
+        <v>91415.00</v>
       </c>
       <c r="I7" s="65">
         <v>0</v>
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="66">
-        <v>-0.20</v>
+        <v>-1.00</v>
       </c>
       <c r="N7" s="63">
-        <v>73384</v>
+        <v>91414</v>
       </c>
       <c r="O7" s="65">
         <v>0</v>
@@ -605,19 +605,19 @@
         </is>
       </c>
       <c r="D8" s="63">
-        <v>120879</v>
+        <v>144027</v>
       </c>
       <c r="E8" s="65">
         <v>0</v>
       </c>
       <c r="F8" s="63">
-        <v>120879</v>
+        <v>144027</v>
       </c>
       <c r="G8" s="65">
         <v>0</v>
       </c>
       <c r="H8" s="66">
-        <v>120879.00</v>
+        <v>144027.00</v>
       </c>
       <c r="I8" s="65">
         <v>0</v>
@@ -635,7 +635,7 @@
         <v>0.00</v>
       </c>
       <c r="N8" s="63">
-        <v>120879</v>
+        <v>144027</v>
       </c>
       <c r="O8" s="65">
         <v>0</v>
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="D9" s="63">
-        <v>316281</v>
-      </c>
-      <c r="E9" s="63">
-        <v>1332</v>
-      </c>
-      <c r="F9" s="63">
-        <v>314949</v>
+        <v>411142</v>
+      </c>
+      <c r="E9" s="64">
+        <v>2170.10</v>
+      </c>
+      <c r="F9" s="64">
+        <v>408971.90</v>
       </c>
       <c r="G9" s="65">
         <v>0</v>
       </c>
       <c r="H9" s="66">
-        <v>314949.00</v>
+        <v>408971.90</v>
       </c>
       <c r="I9" s="65">
         <v>0</v>
@@ -688,10 +688,10 @@
         <v>0</v>
       </c>
       <c r="M9" s="66">
-        <v>-4.00</v>
+        <v>-3.90</v>
       </c>
       <c r="N9" s="63">
-        <v>314945</v>
+        <v>408968</v>
       </c>
       <c r="O9" s="65">
         <v>0</v>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="D10" s="63">
-        <v>280659</v>
+        <v>304567</v>
       </c>
       <c r="E10" s="66">
         <v>808.80</v>
       </c>
       <c r="F10" s="64">
-        <v>279850.20</v>
+        <v>303758.20</v>
       </c>
       <c r="G10" s="65">
         <v>0</v>
       </c>
       <c r="H10" s="66">
-        <v>279850.20</v>
+        <v>303758.20</v>
       </c>
       <c r="I10" s="65">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>-0.20</v>
       </c>
       <c r="N10" s="63">
-        <v>279850</v>
+        <v>303758</v>
       </c>
       <c r="O10" s="65">
         <v>0</v>
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="D11" s="2">
-        <v>971712.00</v>
+        <v>1159141.00</v>
       </c>
       <c r="E11" s="2">
-        <v>2658.10</v>
+        <v>3546.80</v>
       </c>
       <c r="F11" s="2">
-        <v>969053.90</v>
+        <v>1155594.20</v>
       </c>
       <c r="G11" s="2">
         <v>0.00</v>
       </c>
       <c r="H11" s="2">
-        <v>969053.90</v>
+        <v>1155594.20</v>
       </c>
       <c r="I11" s="2">
         <v>0.00</v>
@@ -795,10 +795,10 @@
         <v>0.00</v>
       </c>
       <c r="M11" s="2">
-        <v>-5.90</v>
+        <v>-6.20</v>
       </c>
       <c r="N11" s="2">
-        <v>969048.00</v>
+        <v>1155588.00</v>
       </c>
       <c r="O11" s="2">
         <v>0.00</v>
